--- a/data_hei/batch-20260930-0015/results.xlsx
+++ b/data_hei/batch-20260930-0015/results.xlsx
@@ -1107,7 +1107,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>name, email, phone found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -18892,7 +18892,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -18959,7 +18959,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -19026,7 +19026,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -19227,7 +19227,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -21893,7 +21893,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -21950,7 +21950,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -22007,7 +22007,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>quote found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>name, email, phone found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -22929,7 +22929,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>name, email, phone found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -23220,7 +23220,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>name, email found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -23275,7 +23275,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>name found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>

--- a/data_hei/batch-20260930-0015/results.xlsx
+++ b/data_hei/batch-20260930-0015/results.xlsx
@@ -671,25 +671,37 @@
           <t>Cologne Business School</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Katrin Steinhoff</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Executive Education</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>katrin.steinhoff@uni-koeln.de</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>https://business-school.uni-koeln.de/de/</t>
+          <t>https://business-school.uni-koeln.de/de/seminare/leadership-change-management</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -750,16 +762,36 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>+49 (0)221 470 76345</t>
+        </is>
+      </c>
+      <c r="AD2" s="1" t="inlineStr">
+        <is>
+          <t>https://business-school.uni-koeln.de/de/seminare/leadership-change-management</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Katrin Steinhoff ... Executive Education</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>no contact found</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+          <t>name, email, phone found on page</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Secretary / administration (last resort). Katrin Steinhoff works in Executive Education with a listed email and phone number.</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>contact_name;email</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
           <t>5</t>
@@ -789,15 +821,19 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>site found via: web search (DuckDuckGo). mode: gemini. 6 page(s) could not be read.</t>
+          <t>site found via: remembered from an earlier run. mode: gemini. 23 page(s) could not be read.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:10Z</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+          <t>2026-10-22T20:04:40Z</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>AI-read</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2319,54 +2355,56 @@
     </row>
   </sheetData>
   <hyperlinks>
+    <hyperlink ref="B2" location="'Contacts'!A2" display="Katrin Steinhoff"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId1"/>
     <hyperlink ref="M2" location="'r001 Cologne Business School'!A1" display="4"/>
     <hyperlink ref="N2" location="'r001 Cologne Business School'!A1" display="1"/>
-    <hyperlink ref="B3" location="'Contacts'!A2" display="Andrea Gommans"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD2" r:id="rId2"/>
+    <hyperlink ref="B3" location="'Contacts'!A3" display="Andrea Gommans"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId3"/>
     <hyperlink ref="M3" location="'r002 ESCP Business School'!A1" display="30"/>
     <hyperlink ref="N3" location="'r002 ESCP Business School'!A1" display="7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD3" r:id="rId4"/>
-    <hyperlink ref="B4" location="'Contacts'!A3" display="Oficina de Atención Internacional"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD3" r:id="rId5"/>
+    <hyperlink ref="B4" location="'Contacts'!A4" display="Oficina de Atención Internacional"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId6"/>
     <hyperlink ref="M4" location="'r003 University of Oviedo'!A1" display="9"/>
     <hyperlink ref="N4" location="'r003 University of Oviedo'!A1" display="5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="rId7"/>
-    <hyperlink ref="B5" location="'Contacts'!A5" display="Erasmus Office"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD4" r:id="rId8"/>
+    <hyperlink ref="B5" location="'Contacts'!A6" display="Erasmus Office"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId9"/>
     <hyperlink ref="M5" location="'r004 European University Cyprus'!A1" display="51"/>
     <hyperlink ref="N5" location="'r004 European University Cyprus'!A1" display="3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD5" r:id="rId10"/>
-    <hyperlink ref="B6" location="'Contacts'!A6" display="Michał Zając"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD5" r:id="rId11"/>
+    <hyperlink ref="B6" location="'Contacts'!A7" display="Michał Zając"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId12"/>
     <hyperlink ref="M6" location="'r005 University of Warsaw'!A1" display="65"/>
     <hyperlink ref="N6" location="'r005 University of Warsaw'!A1" display="2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD6" r:id="rId13"/>
-    <hyperlink ref="B7" location="'Contacts'!A8" display="Břetislav Dančák"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD6" r:id="rId14"/>
+    <hyperlink ref="B7" location="'Contacts'!A9" display="Břetislav Dančák"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId15"/>
     <hyperlink ref="M7" location="'r006 Masaryk University'!A1" display="10"/>
     <hyperlink ref="N7" location="'r006 Masaryk University'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD7" r:id="rId15"/>
-    <hyperlink ref="B8" location="'Contacts'!A9" display="Dalius Jatužis"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD7" r:id="rId16"/>
+    <hyperlink ref="B8" location="'Contacts'!A10" display="Dalius Jatužis"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId17"/>
     <hyperlink ref="M8" location="'r007 Vilnius University'!A1" display="8"/>
     <hyperlink ref="N8" location="'r007 Vilnius University'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD8" r:id="rId17"/>
-    <hyperlink ref="B9" location="'Contacts'!A11" display="Bibi Ovaska"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD8" r:id="rId18"/>
+    <hyperlink ref="B9" location="'Contacts'!A12" display="Bibi Ovaska"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId19"/>
     <hyperlink ref="M9" location="'r008 University of Ljubljana'!A1" display="16"/>
     <hyperlink ref="N9" location="'r008 University of Ljubljana'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD9" r:id="rId19"/>
-    <hyperlink ref="B11" location="'Contacts'!A12" display="Inge van Haare"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD9" r:id="rId20"/>
+    <hyperlink ref="B11" location="'Contacts'!A13" display="Inge van Haare"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId21"/>
     <hyperlink ref="M11" location="'r010 University of Twente'!A1" display="11"/>
     <hyperlink ref="N11" location="'r010 University of Twente'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD11" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD11" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7511,7 +7549,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:10Z</t>
+          <t>2026-10-22T20:04:40Z</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7616,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:10Z</t>
+          <t>2026-10-22T20:04:40Z</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7683,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:10Z</t>
+          <t>2026-10-22T20:04:40Z</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7750,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:10Z</t>
+          <t>2026-10-22T20:04:40Z</t>
         </is>
       </c>
     </row>
@@ -21442,7 +21480,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:10Z</t>
+          <t>2026-10-22T20:04:40Z</t>
         </is>
       </c>
     </row>
@@ -22678,7 +22716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22751,12 +22789,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>r002</t>
+          <t>r001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESCP Business School</t>
+          <t>Cologne Business School</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -22766,34 +22804,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Andrea Gommans</t>
+          <t>Katrin Steinhoff</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Erasmus+ coordinator</t>
+          <t>Executive Education</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>erasmus.berlin@escp.eu</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>katrin.steinhoff@uni-koeln.de</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>+49 (0)221 470 76345</t>
+        </is>
+      </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://escp.eu/international/erasmus</t>
+          <t>https://business-school.uni-koeln.de/de/seminare/leadership-change-management</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>The selection is made centrally by the Erasmus+ coordinator. The selection criteria are divided into qualitative and formal criteria. The formal criteria are completeness of the documents, accuracy of the information, plausibility of the information, compliance with the formal requirements and deadlines or, if applicable, the agreements made. The qualitative criteria are professional motivation for the internship and the embedding of the internship in the course of the study. ... Andrea Gommans</t>
+          <t>Katrin Steinhoff ... Executive Education</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Institutional Erasmus+ coordinator. Andrea Gommans is explicitly identified as the Erasmus+ coordinator responsible for the selection process and providing advice on applications.</t>
+          <t>Secretary / administration (last resort). Katrin Steinhoff works in Executive Education with a listed email and phone number.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -22803,19 +22845,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>name, email, phone found on page</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>r003</t>
+          <t>r002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>University of Oviedo</t>
+          <t>ESCP Business School</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -22825,38 +22867,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Oficina de Atención Internacional</t>
+          <t>Andrea Gommans</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>International Welcome Office</t>
+          <t>Erasmus+ coordinator</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>inter.incoming@uniovi.es</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>985 10 40 41</t>
-        </is>
-      </c>
+          <t>erasmus.berlin@escp.eu</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.uniovi.es/conocenos/servicios/internacionalizacion</t>
+          <t>https://escp.eu/international/erasmus</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Oficina de Atención Internacional (Estudiantes entrantes)</t>
+          <t>The selection is made centrally by the Erasmus+ coordinator. The selection criteria are divided into qualitative and formal criteria. The formal criteria are completeness of the documents, accuracy of the information, plausibility of the information, compliance with the formal requirements and deadlines or, if applicable, the agreements made. The qualitative criteria are professional motivation for the internship and the embedding of the internship in the course of the study. ... Andrea Gommans</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>International relations officer. This office provides support and information for incoming international students.</t>
+          <t>Institutional Erasmus+ coordinator. Andrea Gommans is explicitly identified as the Erasmus+ coordinator responsible for the selection process and providing advice on applications.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -22883,28 +22921,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sección de Programas Internacionales</t>
+          <t>Oficina de Atención Internacional</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>International Programs Section</t>
+          <t>International Welcome Office</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>inter.movilidad@uniovi.es</t>
+          <t>inter.incoming@uniovi.es</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>985 10 40 28</t>
+          <t>985 10 40 41</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
@@ -22914,12 +22952,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sección de Programas Internacionales</t>
+          <t>Oficina de Atención Internacional (Estudiantes entrantes)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Mobility coordinator. This section manages international mobility programs and student exchanges.</t>
+          <t>International relations officer. This office provides support and information for incoming international students.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -22936,49 +22974,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>r004</t>
+          <t>r003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>European University Cyprus</t>
+          <t>University of Oviedo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erasmus Office</t>
+          <t>Sección de Programas Internacionales</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Erasmus Office</t>
+          <t>International Programs Section</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>erasmus@euc.ac.cy</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>inter.movilidad@uniovi.es</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>985 10 40 28</t>
+        </is>
+      </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>https://euc.ac.cy/wp-content/uploads/2026/08/Erasmus-Before-During-After-mobility-documentation.pdf</t>
+          <t>https://www.uniovi.es/conocenos/servicios/internacionalizacion</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>e. The Contact Person is the Erasmus Office, erasmus@euc.ac.cy.</t>
+          <t>Sección de Programas Internacionales</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Mobility coordinator. The Erasmus Office is the central contact point for all Erasmus+ mobility inquiries and documentation.</t>
+          <t>Mobility coordinator. This section manages international mobility programs and student exchanges.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -22995,12 +23037,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>r005</t>
+          <t>r004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>University of Warsaw</t>
+          <t>European University Cyprus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23010,34 +23052,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Michał Zając</t>
+          <t>Erasmus Office</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mobility Coordinator</t>
+          <t>Erasmus Office</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>michal.zajac@uw.edu.pl</t>
+          <t>erasmus@euc.ac.cy</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://www.wdib.uw.edu.pl/pracownicy/erasmus-plus-dla-pracownikow</t>
+          <t>https://euc.ac.cy/wp-content/uploads/2026/08/Erasmus-Before-During-After-mobility-documentation.pdf</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pełnomocnik ds. mobilności studentów i pracowników ... dr Michał Zając</t>
+          <t>e. The Contact Person is the Erasmus Office, erasmus@euc.ac.cy.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Mobility coordinator. He is the designated Mobility Coordinator for the Faculty of Journalism, Information and Book Studies.</t>
+          <t>Mobility coordinator. The Erasmus Office is the central contact point for all Erasmus+ mobility inquiries and documentation.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -23064,39 +23106,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Michał Głowacki</t>
+          <t>Michał Zając</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deputy Dean for Research and International Collaboration</t>
+          <t>Mobility Coordinator</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>michal.glowacki@uw.edu.pl</t>
+          <t>michal.zajac@uw.edu.pl</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>https://www.wdib.uw.edu.pl/in-english#research-support</t>
+          <t>https://www.wdib.uw.edu.pl/pracownicy/erasmus-plus-dla-pracownikow</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Professor Michał Głowacki, PhD ... Deputy Dean for Research and International Collaboration</t>
+          <t>Pełnomocnik ds. mobilności studentów i pracowników ... dr Michał Zając</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Vice-rector for international affairs. He holds the senior faculty role responsible for international collaboration.</t>
+          <t>Mobility coordinator. He is the designated Mobility Coordinator for the Faculty of Journalism, Information and Book Studies.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -23113,45 +23155,49 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>r006</t>
+          <t>r005</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Masaryk University</t>
+          <t>University of Warsaw</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Břetislav Dančák</t>
+          <t>Michał Głowacki</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vice-Rector for Internationalization</t>
+          <t>Deputy Dean for Research and International Collaboration</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>michal.glowacki@uw.edu.pl</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>https://www.muni.cz/pro-media/tiskove-zpravy/dobrovolnicke-centrum-masarykovy-univerzity-muni-pomaha-ziskalo-od-evropske-asociace-pro-mezinarodni-vzdelavani-eaie-cenu-za-vynikajici-pristup-v-oblasti-internacionalizace</t>
+          <t>https://www.wdib.uw.edu.pl/in-english#research-support</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>„Globální pandemie Covidu odstartovala naprosto unikátní aktivitu, která se přetavila v budoucí pomoc Ukrajině. A tato cena je důkazem obrovského dopadu naší činnosti do mezinárodní komunity, neboť je udělována pouze vysokoškolským institucím, které prokázaly vynikající výsledky v této oblasti a úspěšně realizovaly strategie a aktivity v oblasti internacionalizace,“ dodává prorektor pro internacionalizaci MU Břetislav Dančák.</t>
+          <t>Professor Michał Głowacki, PhD ... Deputy Dean for Research and International Collaboration</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Vice-rector for international affairs. He is the Vice-Rector for Internationalization at Masaryk University.</t>
+          <t>Vice-rector for international affairs. He holds the senior faculty role responsible for international collaboration.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -23168,12 +23214,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>r007</t>
+          <t>r006</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vilnius University</t>
+          <t>Masaryk University</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23183,34 +23229,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dalius Jatužis</t>
+          <t>Břetislav Dančák</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dean of the Faculty of Medicine</t>
+          <t>Vice-Rector for Internationalization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>dalius.jatuzis@mf.vu.lt</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>https://www.vu.lt/visos-naujienos/vu-medicinos-fakultetas-stiprina-tarptautinius-rysius-demesys-partnerystei-su-turkija</t>
+          <t>https://www.muni.cz/pro-media/tiskove-zpravy/dobrovolnicke-centrum-masarykovy-univerzity-muni-pomaha-ziskalo-od-evropske-asociace-pro-mezinarodni-vzdelavani-eaie-cenu-za-vynikajici-pristup-v-oblasti-internacionalizace</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Cengiz Gunes, prof. Dalius Jatužis, Turkijos ambasadorė Lietuvoje Esra Toplu, doc. Laura Nedzinskienė, dr. Aleksas Pikturna. VU Medicinos fakulteto archyvo nuotr.Vilniaus universiteto (VU) Medicinos fakultete (MF) lankėsi Turkijos ambasadorė Lietuvoje Esra Toplu kartu su patarėju Cengizu Güneşu. Garbius svečius priėmė VU Medicinos fakulteto dekanas prof. Dalius Jatužis, prodekanai doc. Laura Nedzinskienė ir dr. Aleksas Pikturna.</t>
+          <t>„Globální pandemie Covidu odstartovala naprosto unikátní aktivitu, která se přetavila v budoucí pomoc Ukrajině. A tato cena je důkazem obrovského dopadu naší činnosti do mezinárodní komunity, neboť je udělována pouze vysokoškolským institucím, které prokázaly vynikající výsledky v této oblasti a úspěšně realizovaly strategie a aktivity v oblasti internacionalizace,“ dodává prorektor pro internacionalizaci MU Břetislav Dančák.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Principal / director (no Erasmus contact found). As the Dean of the Faculty of Medicine, he is a key institutional leader involved in international partnerships. Own work email found on a page naming them.</t>
+          <t>Vice-rector for international affairs. He is the Vice-Rector for Internationalization at Masaryk University.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -23237,21 +23279,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Laura Nedzinskienė</t>
+          <t>Dalius Jatužis</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vice-Dean of the Faculty of Medicine</t>
+          <t>Dean of the Faculty of Medicine</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>dalius.jatuzis@mf.vu.lt</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -23265,7 +23311,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Other role. She is a Vice-Dean involved in managing international student relations and partnerships.</t>
+          <t>Principal / director (no Erasmus contact found). As the Dean of the Faculty of Medicine, he is a key institutional leader involved in international partnerships. Own work email found on a page naming them.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -23282,27 +23328,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r008</t>
+          <t>r007</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>University of Ljubljana</t>
+          <t>Vilnius University</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bibi Ovaska</t>
+          <t>Laura Nedzinskienė</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Institutional Erasmus+ Coordinator</t>
+          <t>Vice-Dean of the Faculty of Medicine</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -23310,17 +23356,17 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>https://www.uni-lj.si/assets/Sluzba-za-mednarodno-sodelovanje/Erasmus+/Razpisi/RJavni-razpis-za-kratkorocno-mobilnost-doktorskih-studentov-z-namenom-studija-in/ali-prakse-v-okviru-programa-Erasmus+-2025.pdf</t>
+          <t>https://www.vu.lt/visos-naujienos/vu-medicinos-fakultetas-stiprina-tarptautinius-rysius-demesys-partnerystei-su-turkija</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Ljubljana, 11. 5. 2026 Bibi Ovaska ... Institucionalni koordinator Erasmus+ KA1 131</t>
+          <t>Cengiz Gunes, prof. Dalius Jatužis, Turkijos ambasadorė Lietuvoje Esra Toplu, doc. Laura Nedzinskienė, dr. Aleksas Pikturna. VU Medicinos fakulteto archyvo nuotr.Vilniaus universiteto (VU) Medicinos fakultete (MF) lankėsi Turkijos ambasadorė Lietuvoje Esra Toplu kartu su patarėju Cengizu Güneşu. Garbius svečius priėmė VU Medicinos fakulteto dekanas prof. Dalius Jatužis, prodekanai doc. Laura Nedzinskienė ir dr. Aleksas Pikturna.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Institutional Erasmus+ coordinator. Bibi Ovaska is the Institutional Coordinator for Erasmus+ KA1 131 at the University of Ljubljana.</t>
+          <t>Other role. She is a Vice-Dean involved in managing international student relations and partnerships.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -23337,12 +23383,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r008</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>University of Ljubljana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -23352,42 +23398,97 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Inge van Haare</t>
+          <t>Bibi Ovaska</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Faculty Internationalisation Coordinator</t>
+          <t>Institutional Erasmus+ Coordinator</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>i.vanhaare@utwente.nl</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr">
         <is>
+          <t>https://www.uni-lj.si/assets/Sluzba-za-mednarodno-sodelovanje/Erasmus+/Razpisi/RJavni-razpis-za-kratkorocno-mobilnost-doktorskih-studentov-z-namenom-studija-in/ali-prakse-v-okviru-programa-Erasmus+-2025.pdf</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Ljubljana, 11. 5. 2026 Bibi Ovaska ... Institucionalni koordinator Erasmus+ KA1 131</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Institutional Erasmus+ coordinator. Bibi Ovaska is the Institutional Coordinator for Erasmus+ KA1 131 at the University of Ljubljana.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Inge van Haare</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Faculty Internationalisation Coordinator</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>i.vanhaare@utwente.nl</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
           <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>• Faculty Internationalisation Coordinator → Inge van Haare</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Faculty-level Erasmus/international coordinator. Inge van Haare is the Faculty Internationalisation Coordinator for the BMS faculty and is listed as a key contact for internationalisation strategy.</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
@@ -23406,6 +23507,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_hei/batch-20260930-0015/results.xlsx
+++ b/data_hei/batch-20260930-0015/results.xlsx
@@ -20,7 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r006 Masaryk University" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r007 Vilnius University" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r008 University of Ljubljana" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r010 University of Twente" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r009 Comenius University Bratis" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="r010 University of Twente" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -779,7 +780,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>name, email, phone found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -2067,31 +2068,63 @@
           <t>Comenius University Bratislava</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Milan Remiš</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Head of Erasmus+ office</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>milan.remis@uniba.sk</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>infocentrum@uniba.sk</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/eninternational-relationserasmus/kontakty-oddelenie-programu-erasmus/</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>r009</t>
@@ -2128,46 +2161,90 @@
           <t>contact9@example.com</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/teachers-researchers-mobility/incoming-teachers-researchers-mobility/</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>+421 2 9010 2066</t>
+        </is>
+      </c>
+      <c r="AD10" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/eninternational-relationserasmus/kontakty-oddelenie-programu-erasmus/</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Head of Erasmus+ office ... RNDr. Milan Remiš - SB 101</t>
+        </is>
+      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>no contact found</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
+          <t>name, email, phone found on page</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Institutional Erasmus+ coordinator. He is the Head of the Erasmus+ office and responsible for institutional coordination. Own work email found on a page naming them.</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>contact_name;email</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>57 of 57 verified</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2 verified of ~53 stated (rest of the list not readable)</t>
+        </is>
+      </c>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>website not found</t>
+          <t>The evidence provides a list of bilateral agreements but does not provide a comprehensive list of all Erasmus+ partners. The contact list is focused on the central Rectorate office.</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Website not found (email domain: https://www.example.com/ -&gt; homepage does not mention this institution's name or phone; email domain: https://example.com/ -&gt; homepage does not mention this institution's name or phone; web search (DuckDuckGo): https://uniba.sk/ -&gt; could not read https://uniba.sk/ (URLError: &lt;urlopen error [SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1010)&gt;); web search (DuckDuckGo): https://www.fedu.uniba.sk/ -&gt; could not read https://www.fedu.uniba.sk/ (URLError: &lt;urlopen error [SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1010)&gt;); web search (DuckDuckGo): https://fphil.uniba.sk/ -&gt; could not read https://fphil.uniba.sk/ (URLError: &lt;urlopen error [SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1010)&gt;); web search (DuckDuckGo): https://www.fm.uniba.sk/ -&gt; could not read https://www.fm.uniba.sk/ (URLError: &lt;urlopen error [SSL: SSLV3_ALERT_HANDSHAKE_FAILURE] sslv3 alert handshake failure (_ssl.c:1010)&gt;))</t>
+          <t>site found via: website column in the sheet. mode: gemini.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2026-09-30T07:19:53Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>not read</t>
+          <t>AI-read</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2476,18 @@
     <hyperlink ref="M9" location="'r008 University of Ljubljana'!A1" display="16"/>
     <hyperlink ref="N9" location="'r008 University of Ljubljana'!A1" display="1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD9" r:id="rId20"/>
-    <hyperlink ref="B11" location="'Contacts'!A13" display="Inge van Haare"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId21"/>
+    <hyperlink ref="B10" location="'Contacts'!A13" display="Milan Remiš"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId21"/>
+    <hyperlink ref="M10" location="'r009 Comenius University Bratis'!A1" display="52"/>
+    <hyperlink ref="N10" location="'r009 Comenius University Bratis'!A1" display="2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD10" r:id="rId23"/>
+    <hyperlink ref="B11" location="'Contacts'!A16" display="Inge van Haare"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId24"/>
     <hyperlink ref="M11" location="'r010 University of Twente'!A1" display="11"/>
     <hyperlink ref="N11" location="'r010 University of Twente'!A1" display="1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD11" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AD11" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6840,6 +6923,2174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>← Back to all institutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>International partners (52) - those with no country stated are last</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>International or National?</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Mobility</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Verified?</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Universität Wien</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Karl-Franzes Universität Graz</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gent University</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>St. Kliment Ohridski University Sophia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Carleton University, Ontario</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>University of Ottawa, Ontario</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>University of Zagreb</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Univerzita Karlova, Praha</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Masarykova univerzita, Brno</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Slezská univerzita v Opavě</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Université Blaise Pascal, Clermont Ferrand</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Université Sciences et Technologie, Bordeaux 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Université Victor Segalen, Bordeaux 2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Université Michel de Montaigne, Bordeaux</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Université Marc Bloch, Strasbourg</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Université Paris-Sud XI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Universität Bremen</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Martin Luther Universität, Halle-Wittenberg</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Universität Regensburg</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Aristotle University, Thessaloniki</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>National Kapodistrian University of Athens</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Eötvös Loránd University, Budapest</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tel Aviv University</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>University of Bari</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>University of Padova</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>University of Trieste</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>University of Udine</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Waseda University</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Jagiellonian University, Kraków</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>University of Silesia, Katowice</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>University of Lodz</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Warsaw University</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Lucian Blaga University, Sibiu</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>M. V. Lomonosov State University</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>University of Ljubljana</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Complutense University of Madrid</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bogazici University</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>National Taras Shevchenko University of Kyiv</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Covenant College, Georgia</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>University of Georgia, Georgia</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>University of Northern Iowa, Cedar Falls, Iowa</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>University of New Orleans, Louisiana</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Montclair State University, New Jersey</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>New York University, New York</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Lake Erie College, Ohio</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Indiana University of Pennsylvania, Pennsylvania</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Slippery Rock University, Pennsylvania</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>City University Bellevue, Washington</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ENLIGHT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Université Marc Bloch, Strasbourg- Université Paris-Sud XI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>European Space Agency</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Campuses (2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Verified?</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jessenius Faculty of Medicine</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Institutions'!A10" display="← Back to all institutes"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId54"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7416,7 +9667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M205"/>
+  <dimension ref="A1:M257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20416,12 +22667,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Westfälische Wilhelms-Universität Münster</t>
+          <t>Universität Wien</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -20451,44 +22702,44 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J195" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>5.4 Appendix D: UT’s International Strategic Partners (ISP’s) WWU/Münster, Germany and</t>
+          <t>Universität Wien</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ECIU</t>
+          <t>Karl-Franzes Universität Graz</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -20498,7 +22749,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -20518,44 +22769,44 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J196" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>• Consortia (e.g., ECIU)</t>
+          <t>Karl-Franzes Universität Graz</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Westfälische Wilhelms-Universität Münster (WWU)</t>
+          <t>Gent University</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -20585,44 +22836,44 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J197" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>BMS faculty is coordinating two of these partners for the UT; the Westfälische Wilhelms-Universität</t>
+          <t>Gent University</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>University of Waterloo (UW)</t>
+          <t>St. Kliment Ohridski University Sophia</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -20652,44 +22903,44 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J198" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Münster (WWU) in Germany and the University of Waterloo (UW) in Canada. We are collaborating</t>
+          <t>St. Kliment Ohridski University Sophia</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>European Consortium of Innovative Universities (ECIU)</t>
+          <t>Carleton University, Ontario</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -20699,7 +22950,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -20719,44 +22970,44 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J199" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>online dashboard is being created. The UT is member of the European Consortium of Innovative</t>
+          <t>Carleton University, Ontario</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>WWU</t>
+          <t>University of Ottawa, Ontario</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -20786,44 +23037,44 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J200" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Our faculty currently has International Strategic Partnerships with WWU in Germany and UW in</t>
+          <t>University of Ottawa, Ontario</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Euregio</t>
+          <t>University of Zagreb</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -20833,7 +23084,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -20853,44 +23104,44 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J201" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>international networks, such as Euregio and the Global South, coordination is needed to make sure</t>
+          <t>University of Zagreb</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>European Consortium for Accreditation in higher education</t>
+          <t>Univerzita Karlova, Praha</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -20900,7 +23151,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -20920,44 +23171,44 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J202" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>ECA European Consortium for Accreditation in higher education</t>
+          <t>Univerzita Karlova, Praha</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>European Consortium of Innovative Universities</t>
+          <t>Masarykova univerzita, Brno</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -20967,7 +23218,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -20987,49 +23238,49 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J203" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>ECIU European Consortium of Innovative Universities</t>
+          <t>Masarykova univerzita, Brno</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>University of Waterloo</t>
+          <t>Slezská univerzita v Opavě</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Country not stated</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -21054,97 +23305,3581 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="J204" s="1" t="inlineStr">
         <is>
-          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>UW University of Waterloo</t>
+          <t>Slezská univerzita v Opavě</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>previously verified; page not in this run's cache (reused prior result)</t>
+          <t>quote found on page</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:50Z</t>
+          <t>2026-10-22T22:10:47Z</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
+          <t>Université Blaise Pascal, Clermont Ferrand</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J205" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Université Blaise Pascal, Clermont Ferrand</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Université Sciences et Technologie, Bordeaux 1</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J206" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Université Sciences et Technologie, Bordeaux 1</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Université Victor Segalen, Bordeaux 2</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J207" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Université Victor Segalen, Bordeaux 2</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Université Michel de Montaigne, Bordeaux</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J208" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Université Michel de Montaigne, Bordeaux</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Université Marc Bloch, Strasbourg</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J209" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Université Marc Bloch, Strasbourg- Université Paris-Sud XI</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Université Paris-Sud XI</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J210" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Université Marc Bloch, Strasbourg- Université Paris-Sud XI</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Universität Bremen</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J211" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Universität Bremen</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Martin Luther Universität, Halle-Wittenberg</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J212" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Martin Luther Universität, Halle-Wittenberg</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Universität Regensburg</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J213" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Universität Regensburg</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Aristotle University, Thessaloniki</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J214" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Aristotle University, Thessaloniki</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>National Kapodistrian University of Athens</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J215" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>National Kapodistrian University of Athens</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Eötvös Loránd University, Budapest</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J216" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Eötvös Loránd University, Budapest</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Tel Aviv University</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J217" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Tel Aviv University</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>University of Bari</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J218" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>University of Bari</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>University of Padova</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J219" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>University of Padova</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>University of Trieste</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J220" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>University of Trieste</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>University of Udine</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J221" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>University of Udine</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Waseda University</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J222" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Waseda University</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>The Netherlands</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J223" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>University of Groningen</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Jagiellonian University, Kraków</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J224" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Jagiellonian University, Kraków</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>University of Silesia, Katowice</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J225" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>University of Silesia, Katowice</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>University of Lodz</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J226" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>University of Lodz</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Warsaw University</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J227" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Warsaw University</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Lucian Blaga University, Sibiu</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J228" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Lucian Blaga University, Sibiu</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>M. V. Lomonosov State University</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J229" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>M. V. Lomonosov State University - from 24.2.2022 - cooperation suspended</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>University of Ljubljana</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J230" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>University of Ljubljana</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Complutense University of Madrid</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J231" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Complutense University of Madrid</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Bogazici University</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J232" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Bogazici University</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>National Taras Shevchenko University of Kyiv</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J233" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>National Taras Shevchenko University of Kyiv</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Covenant College, Georgia</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J234" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Covenant College, Georgia</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>University of Georgia, Georgia</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J235" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>University of Georgia, Georgia</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>University of Northern Iowa, Cedar Falls, Iowa</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J236" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>University of Northern Iowa, Cedar Falls, Iowa</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>University of New Orleans, Louisiana</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J237" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>University of New Orleans, Louisiana</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Montclair State University, New Jersey</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J238" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Montclair State University, New Jersey</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>New York University, New York</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J239" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>New York University, New York</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Lake Erie College, Ohio</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>college</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J240" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Lake Erie College, Ohio</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Indiana University of Pennsylvania, Pennsylvania</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J241" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Indiana University of Pennsylvania, Pennsylvania</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Slippery Rock University, Pennsylvania</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J242" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Slippery Rock University, Pennsylvania</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>City University Bellevue, Washington</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J243" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>City University Bellevue, Washington (a special agreement)</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>ENLIGHT</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J244" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>ENLIGHT</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Université Marc Bloch, Strasbourg- Université Paris-Sud XI</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J245" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/university-cooperation-mobility/bilateral-cooperation/bilateral-agreements/</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Université Marc Bloch, Strasbourg- Université Paris-Sud XI</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>European Space Agency</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="J246" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Slovak scientists from Comenius University Bratislava have once again made history in space safety research. They took part in ROSIE, an international airborne expedition supported by the European Space Agency (ESA), to document the controlled re-entry and break-up of two satellites at close range over the South Pacific.</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Westfälische Wilhelms-Universität Münster</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J247" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>5.4 Appendix D: UT’s International Strategic Partners (ISP’s) WWU/Münster, Germany and</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>ECIU</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J248" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>• Consortia (e.g., ECIU)</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Westfälische Wilhelms-Universität Münster (WWU)</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J249" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>BMS faculty is coordinating two of these partners for the UT; the Westfälische Wilhelms-Universität</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>University of Waterloo (UW)</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J250" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Münster (WWU) in Germany and the University of Waterloo (UW) in Canada. We are collaborating</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>European Consortium of Innovative Universities (ECIU)</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J251" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>online dashboard is being created. The UT is member of the European Consortium of Innovative</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>WWU</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J252" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Our faculty currently has International Strategic Partnerships with WWU in Germany and UW in</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Euregio</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J253" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>international networks, such as Euregio and the Global South, coordination is needed to make sure</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>European Consortium for Accreditation in higher education</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J254" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>ECA European Consortium for Accreditation in higher education</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>European Consortium of Innovative Universities</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J255" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>ECIU European Consortium of Innovative Universities</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>University of Waterloo</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Country not stated</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="J256" s="1" t="inlineStr">
+        <is>
+          <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>UW University of Waterloo</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-09-30T07:21:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
           <t>School for Millennials</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
         <is>
           <t>Country not stated</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
         <is>
           <t>r010</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I257" t="inlineStr">
         <is>
           <t>University of Twente</t>
         </is>
       </c>
-      <c r="J205" s="1" t="inlineStr">
+      <c r="J257" s="1" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="K257" t="inlineStr">
         <is>
           <t>host a Diversity and Inclusion workshop by 3310-School for Millennials,</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="L257" t="inlineStr">
         <is>
           <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr">
+      <c r="M257" t="inlineStr">
         <is>
           <t>2026-09-30T07:21:50Z</t>
         </is>
@@ -21356,6 +27091,58 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J203" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J204" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="rId256"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21367,7 +27154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22627,55 +28414,169 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bratislava</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Jessenius Faculty of Medicine</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>branch</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>In late September 2026, the Jessenius Faculty of Medicine in Martin, Comenius University Bratislava (JFMED CU), welcomed more than 200 participants and nearly...</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>quote found on page</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-10-22T22:10:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>r010</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>University of Twente</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>University of Twente</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Enschede</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>https://www.utwente.nl</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Je studententijd is meer dan met je neus in de boeken zitten of in de bibliotheek studeren voor je aankomende tentamens. Zie jij jezelf al in een studententeam? Bij een vereniging? Of leef je je liever uit op het veld, samen met je vrienden?️ Hoe je het ook voor je ziet: op de campus van de Universiteit Twente in Enschede haal jij het maximale uit je studententijd!</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>2026-09-30T07:21:50Z</t>
         </is>
@@ -22705,6 +28606,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22716,7 +28619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22845,7 +28748,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>name, email, phone found on page</t>
+          <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
       </c>
     </row>
@@ -23438,12 +29341,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>r010</t>
+          <t>r009</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>University of Twente</t>
+          <t>Comenius University Bratislava</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -23453,42 +29356,223 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Inge van Haare</t>
+          <t>Milan Remiš</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Faculty Internationalisation Coordinator</t>
+          <t>Head of Erasmus+ office</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
+          <t>milan.remis@uniba.sk</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>+421 2 9010 2066</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/eninternational-relationserasmus/kontakty-oddelenie-programu-erasmus/</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Head of Erasmus+ office ... RNDr. Milan Remiš - SB 101</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Institutional Erasmus+ coordinator. He is the Head of the Erasmus+ office and responsible for institutional coordination. Own work email found on a page naming them.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>name, email, phone found on page</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Terézia Tóthová</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Incoming students / Erasmus KA2 projects (partnerships)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>+421 2 9010 2151</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/eninternational-relationserasmus/kontakty-oddelenie-programu-erasmus/</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Incoming students / Erasmus KA2 projects (partnerships) ... Ing. Terézia Tóthová - SB 102</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>International relations officer. She manages incoming students and Erasmus KA2 partnerships.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>name, phone found on page</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>r009</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Comenius University Bratislava</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oliver Vavro</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Staff and teacher mobilities (STT &amp; STA action) / International Credit Mobility (ICM)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>+421 2 9010 2022</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://uniba.sk/en/international-relations/eninternational-relationserasmus/kontakty-oddelenie-programu-erasmus/</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Staff and teacher mobilities (STT &amp; STA action) / International Credit Mobility (ICM) ... Mgr. Oliver Vavro - SB 104</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Mobility coordinator. He coordinates staff and teacher mobilities and International Credit Mobility.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>name, phone found on page</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>r010</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>University of Twente</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Inge van Haare</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Faculty Internationalisation Coordinator</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>i.vanhaare@utwente.nl</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>https://www.utwente.nl/en/bms/education/bms-international-affairs-and-mobility/bms-internationalisation-strategy-2022-2030.pdf</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>• Faculty Internationalisation Coordinator → Inge van Haare</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Faculty-level Erasmus/international coordinator. Inge van Haare is the Faculty Internationalisation Coordinator for the BMS faculty and is listed as a key contact for internationalisation strategy.</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>previously verified; page not in this run's cache (reused prior result)</t>
         </is>
@@ -23508,6 +29592,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
